--- a/materials/解答例/解答例_演習10_見積試算.xlsx
+++ b/materials/解答例/解答例_演習10_見積試算.xlsx
@@ -445,22 +445,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G23"/>
+  <dimension ref="A1:G27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>見積試算（みなと精機 若手技術者向けDX基礎研修）【解答例】</t>
+          <t>見積試算（みらい商事 法人営業向け生成AI活用研修）A案・B案【解答例】</t>
         </is>
       </c>
     </row>
@@ -472,10 +472,14 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>値</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="n"/>
+          <t>A案</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>B案</t>
+        </is>
+      </c>
       <c r="D3" s="2" t="n"/>
       <c r="E3" s="2" t="n"/>
       <c r="F3" s="2" t="n"/>
@@ -488,168 +492,163 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>60</v>
+        <v>20</v>
+      </c>
+      <c r="C4" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>クラス数</t>
-        </is>
-      </c>
-      <c r="B5">
-        <f>ROUNDUP(B4/20,0)</f>
-        <v/>
+          <t>日数</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>1クラスあたり日数</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>3</v>
+          <t>実施形式（集合／オンライン）</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>集合</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>集合</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>実施形式（集合／オンライン）</t>
+          <t>会場（顧客会場／ELI会場）</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>集合</t>
+          <t>顧客会場</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>顧客会場</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>会場（顧客会場／ELI会場）</t>
+          <t>アシスタント講師（あり／なし）</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>顧客会場</t>
+          <t>あり</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>研修カスタマイズ（あり／なし）</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>あり</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>事後フォローアップ（あり／なし）</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>なし</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
         <is>
           <t>コード</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B12" s="3" t="inlineStr">
         <is>
           <t>項目</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="C12" s="3" t="inlineStr">
         <is>
           <t>単価</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
-        <is>
-          <t>数量</t>
-        </is>
-      </c>
-      <c r="E10" s="3" t="inlineStr">
-        <is>
-          <t>小計</t>
-        </is>
-      </c>
-      <c r="F10" s="3" t="inlineStr">
-        <is>
-          <t>割引</t>
-        </is>
-      </c>
-      <c r="G10" s="3" t="inlineStr">
-        <is>
-          <t>金額</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>P01</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>講師料</t>
-        </is>
-      </c>
-      <c r="C11" s="5" t="n">
-        <v>250000</v>
-      </c>
-      <c r="D11" s="5">
-        <f>B5*B6</f>
-        <v/>
-      </c>
-      <c r="E11" s="5">
-        <f>C11*D11</f>
-        <v/>
-      </c>
-      <c r="F11" s="5">
-        <f>IF(B5&gt;=3,E11*0.05,0)</f>
-        <v/>
-      </c>
-      <c r="G11" s="5">
-        <f>E11-F11</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>P02</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>アシスタント講師料</t>
-        </is>
-      </c>
-      <c r="C12" s="5" t="n">
-        <v>80000</v>
-      </c>
-      <c r="D12" s="5">
-        <f>B5*B6</f>
-        <v/>
-      </c>
-      <c r="E12" s="5">
-        <f>C12*D12</f>
-        <v/>
-      </c>
-      <c r="F12" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" s="5">
-        <f>E12-F12</f>
-        <v/>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>A案 数量</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>A案 金額</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>B案 数量</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr">
+        <is>
+          <t>B案 金額</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>P03</t>
+          <t>P01</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>教材費</t>
+          <t>講師料</t>
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>5000</v>
+        <v>250000</v>
       </c>
       <c r="D13" s="5">
-        <f>B4*B6</f>
+        <f>B5</f>
         <v/>
       </c>
       <c r="E13" s="5">
@@ -657,213 +656,316 @@
         <v/>
       </c>
       <c r="F13" s="5">
-        <f>IF(B4&gt;=50,E13*0.1,0)</f>
+        <f>C5</f>
         <v/>
       </c>
       <c r="G13" s="5">
-        <f>E13-F13</f>
+        <f>C13*F13</f>
         <v/>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>P04</t>
+          <t>P02</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>研修カスタマイズ費</t>
+          <t>アシスタント講師料</t>
         </is>
       </c>
       <c r="C14" s="5" t="n">
-        <v>400000</v>
-      </c>
-      <c r="D14" s="5" t="n">
-        <v>1</v>
+        <v>80000</v>
+      </c>
+      <c r="D14" s="5">
+        <f>IF(B8="あり",B5,0)</f>
+        <v/>
       </c>
       <c r="E14" s="5">
         <f>C14*D14</f>
         <v/>
       </c>
-      <c r="F14" s="5" t="n">
-        <v>0</v>
+      <c r="F14" s="5">
+        <f>IF(C8="あり",C5,0)</f>
+        <v/>
       </c>
       <c r="G14" s="5">
-        <f>E14-F14</f>
+        <f>C14*F14</f>
         <v/>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>P05</t>
+          <t>P03</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>事前アセスメント</t>
+          <t>教材費</t>
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>3000</v>
+        <v>5000</v>
       </c>
       <c r="D15" s="5">
-        <f>B4</f>
+        <f>B4*B5</f>
         <v/>
       </c>
       <c r="E15" s="5">
         <f>C15*D15</f>
         <v/>
       </c>
-      <c r="F15" s="5" t="n">
-        <v>0</v>
+      <c r="F15" s="5">
+        <f>C4*C5</f>
+        <v/>
       </c>
       <c r="G15" s="5">
-        <f>E15-F15</f>
+        <f>C15*F15</f>
         <v/>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>P06</t>
+          <t>P04</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>効果測定フォローアップ</t>
+          <t>研修カスタマイズ費</t>
         </is>
       </c>
       <c r="C16" s="5" t="n">
         <v>200000</v>
       </c>
-      <c r="D16" s="5" t="n">
-        <v>1</v>
+      <c r="D16" s="5">
+        <f>IF(B9="あり",1,0)</f>
+        <v/>
       </c>
       <c r="E16" s="5">
         <f>C16*D16</f>
         <v/>
       </c>
-      <c r="F16" s="5" t="n">
-        <v>0</v>
+      <c r="F16" s="5">
+        <f>IF(C9="あり",1,0)</f>
+        <v/>
       </c>
       <c r="G16" s="5">
-        <f>E16-F16</f>
+        <f>C16*F16</f>
         <v/>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>P07</t>
+          <t>P05</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>ELI会場使用料</t>
+          <t>事前アセスメント</t>
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>60000</v>
+        <v>3000</v>
       </c>
       <c r="D17" s="5">
-        <f>IF(B8="ELI会場",B5*B6,0)</f>
+        <f>B4</f>
         <v/>
       </c>
       <c r="E17" s="5">
         <f>C17*D17</f>
         <v/>
       </c>
-      <c r="F17" s="5" t="n">
-        <v>0</v>
+      <c r="F17" s="5">
+        <f>C4</f>
+        <v/>
       </c>
       <c r="G17" s="5">
-        <f>E17-F17</f>
+        <f>C17*F17</f>
         <v/>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>P08</t>
+          <t>P06</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>オンライン配信運営費</t>
+          <t>事後フォローアップ</t>
         </is>
       </c>
       <c r="C18" s="5" t="n">
-        <v>50000</v>
+        <v>100000</v>
       </c>
       <c r="D18" s="5">
-        <f>IF(B7="オンライン",B5*B6,0)</f>
+        <f>IF(B10="あり",1,0)</f>
         <v/>
       </c>
       <c r="E18" s="5">
         <f>C18*D18</f>
         <v/>
       </c>
-      <c r="F18" s="5" t="n">
-        <v>0</v>
+      <c r="F18" s="5">
+        <f>IF(C10="あり",1,0)</f>
+        <v/>
       </c>
       <c r="G18" s="5">
-        <f>E18-F18</f>
+        <f>C18*F18</f>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="4" t="n"/>
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>P07</t>
+        </is>
+      </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>合計（税別）</t>
-        </is>
-      </c>
-      <c r="C19" s="5" t="n"/>
-      <c r="D19" s="5" t="n"/>
-      <c r="E19" s="5" t="n"/>
-      <c r="F19" s="5" t="n"/>
+          <t>ELI会場使用料</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="n">
+        <v>60000</v>
+      </c>
+      <c r="D19" s="5">
+        <f>IF(B7="ELI会場",B5,0)</f>
+        <v/>
+      </c>
+      <c r="E19" s="5">
+        <f>C19*D19</f>
+        <v/>
+      </c>
+      <c r="F19" s="5">
+        <f>IF(C7="ELI会場",C5,0)</f>
+        <v/>
+      </c>
       <c r="G19" s="5">
-        <f>SUM(G11:G18)</f>
+        <f>C19*F19</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="4" t="n"/>
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>P08</t>
+        </is>
+      </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>予算（税別）</t>
-        </is>
-      </c>
-      <c r="C20" s="5" t="n"/>
-      <c r="D20" s="5" t="n"/>
-      <c r="E20" s="5" t="n"/>
-      <c r="F20" s="5" t="n"/>
-      <c r="G20" s="5" t="n">
-        <v>6000000</v>
+          <t>オンライン配信運営費</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="n">
+        <v>50000</v>
+      </c>
+      <c r="D20" s="5">
+        <f>IF(B6="オンライン",B5,0)</f>
+        <v/>
+      </c>
+      <c r="E20" s="5">
+        <f>C20*D20</f>
+        <v/>
+      </c>
+      <c r="F20" s="5">
+        <f>IF(C6="オンライン",C5,0)</f>
+        <v/>
+      </c>
+      <c r="G20" s="5">
+        <f>C20*F20</f>
+        <v/>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="n"/>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>予算との差額</t>
+          <t>割引（2日以上で講師料5%）</t>
         </is>
       </c>
       <c r="C21" s="5" t="n"/>
       <c r="D21" s="5" t="n"/>
-      <c r="E21" s="5" t="n"/>
+      <c r="E21" s="5">
+        <f>IF(B5&gt;=2,-E13*0.05,0)</f>
+        <v/>
+      </c>
       <c r="F21" s="5" t="n"/>
       <c r="G21" s="5">
-        <f>G20-G19</f>
+        <f>IF(C5&gt;=2,-G13*0.05,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="n"/>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>合計（税別）</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="n"/>
+      <c r="D22" s="5" t="n"/>
+      <c r="E22" s="5">
+        <f>SUM(E13:E21)</f>
+        <v/>
+      </c>
+      <c r="F22" s="5" t="n"/>
+      <c r="G22" s="5">
+        <f>SUM(G13:G21)</f>
         <v/>
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>想定合計：4,447,500円（税別）。予算内に約155万円の余裕 → オプション（ハイブリッド型・事後フォロー追加）の提案余地あり</t>
+      <c r="A23" s="4" t="n"/>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>予算の目安（税別・承認前）</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="n"/>
+      <c r="D23" s="5" t="n"/>
+      <c r="E23" s="5" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="F23" s="5" t="n"/>
+      <c r="G23" s="5" t="n">
+        <v>1000000</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="n"/>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>予算との差額（＋は予算内）</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="n"/>
+      <c r="D24" s="5" t="n"/>
+      <c r="E24" s="5">
+        <f>E23-E22</f>
+        <v/>
+      </c>
+      <c r="F24" s="5" t="n"/>
+      <c r="G24" s="5">
+        <f>G23-G22</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>想定：A案 690,000円（予算内・31万円の余裕）／B案 1,195,000円（予算を19.5万円超過）</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>→ B案は「予算の承認額を引き上げる」か「アシスタント講師を外す（▲16万円）」などの調整案を用意して決裁者に説明する</t>
         </is>
       </c>
     </row>

--- a/materials/解答例/解答例_演習10_見積試算.xlsx
+++ b/materials/解答例/解答例_演習10_見積試算.xlsx
@@ -445,7 +445,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G27"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -460,7 +460,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>見積試算（みらい商事 法人営業向け生成AI活用研修）A案・B案【解答例】</t>
+          <t>概算見積（みらい商事 法人営業向け生成AI活用研修）A案・B案【解答例】</t>
         </is>
       </c>
     </row>
@@ -501,154 +501,196 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>日数</t>
+          <t>クラス数</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>1</v>
       </c>
       <c r="C5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>実施形式（集合／オンライン）</t>
+          <t>事前診断（あり／なし）</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>集合</t>
+          <t>なし</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>集合</t>
+          <t>あり</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>会場（顧客会場／ELI会場）</t>
+          <t>活用フォロー（あり／なし）</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>顧客会場</t>
+          <t>なし</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>顧客会場</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>アシスタント講師（あり／なし）</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
           <t>あり</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>研修カスタマイズ（あり／なし）</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>あり</t>
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>コード</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>項目</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>単価</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>A案 数量</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>A案 金額</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>B案 数量</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>B案 金額</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>事後フォローアップ（あり／なし）</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>なし</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>集合研修（2日間）</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>500000</v>
+      </c>
+      <c r="D10" s="5">
+        <f>B5</f>
+        <v/>
+      </c>
+      <c r="E10" s="5">
+        <f>C10*D10</f>
+        <v/>
+      </c>
+      <c r="F10" s="5">
+        <f>C5</f>
+        <v/>
+      </c>
+      <c r="G10" s="5">
+        <f>C10*F10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>P02</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>教材</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>5000</v>
+      </c>
+      <c r="D11" s="5">
+        <f>B4</f>
+        <v/>
+      </c>
+      <c r="E11" s="5">
+        <f>C11*D11</f>
+        <v/>
+      </c>
+      <c r="F11" s="5">
+        <f>C4</f>
+        <v/>
+      </c>
+      <c r="G11" s="5">
+        <f>C11*F11</f>
+        <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>コード</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>項目</t>
-        </is>
-      </c>
-      <c r="C12" s="3" t="inlineStr">
-        <is>
-          <t>単価</t>
-        </is>
-      </c>
-      <c r="D12" s="3" t="inlineStr">
-        <is>
-          <t>A案 数量</t>
-        </is>
-      </c>
-      <c r="E12" s="3" t="inlineStr">
-        <is>
-          <t>A案 金額</t>
-        </is>
-      </c>
-      <c r="F12" s="3" t="inlineStr">
-        <is>
-          <t>B案 数量</t>
-        </is>
-      </c>
-      <c r="G12" s="3" t="inlineStr">
-        <is>
-          <t>B案 金額</t>
-        </is>
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>P03</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>事前診断</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>200000</v>
+      </c>
+      <c r="D12" s="5">
+        <f>IF(B6="あり",1,0)</f>
+        <v/>
+      </c>
+      <c r="E12" s="5">
+        <f>C12*D12</f>
+        <v/>
+      </c>
+      <c r="F12" s="5">
+        <f>IF(C6="あり",1,0)</f>
+        <v/>
+      </c>
+      <c r="G12" s="5">
+        <f>C12*F12</f>
+        <v/>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>P01</t>
+          <t>P04</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>講師料</t>
+          <t>受講後1か月の活用フォロー</t>
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>250000</v>
+        <v>200000</v>
       </c>
       <c r="D13" s="5">
-        <f>B5</f>
+        <f>IF(B7="あり",1,0)</f>
         <v/>
       </c>
       <c r="E13" s="5">
@@ -656,7 +698,7 @@
         <v/>
       </c>
       <c r="F13" s="5">
-        <f>C5</f>
+        <f>IF(C7="あり",1,0)</f>
         <v/>
       </c>
       <c r="G13" s="5">
@@ -665,307 +707,106 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t>P02</t>
-        </is>
-      </c>
+      <c r="A14" s="4" t="n"/>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>アシスタント講師料</t>
-        </is>
-      </c>
-      <c r="C14" s="5" t="n">
-        <v>80000</v>
-      </c>
-      <c r="D14" s="5">
-        <f>IF(B8="あり",B5,0)</f>
-        <v/>
-      </c>
+          <t>合計（税抜）</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n"/>
+      <c r="D14" s="5" t="n"/>
       <c r="E14" s="5">
-        <f>C14*D14</f>
-        <v/>
-      </c>
-      <c r="F14" s="5">
-        <f>IF(C8="あり",C5,0)</f>
-        <v/>
-      </c>
+        <f>SUM(E10:E13)</f>
+        <v/>
+      </c>
+      <c r="F14" s="5" t="n"/>
       <c r="G14" s="5">
-        <f>C14*F14</f>
+        <f>SUM(G10:G13)</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t>P03</t>
-        </is>
-      </c>
+      <c r="A15" s="4" t="n"/>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>教材費</t>
-        </is>
-      </c>
-      <c r="C15" s="5" t="n">
-        <v>5000</v>
-      </c>
-      <c r="D15" s="5">
-        <f>B4*B5</f>
-        <v/>
-      </c>
+          <t>1名あたり</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n"/>
+      <c r="D15" s="5" t="n"/>
       <c r="E15" s="5">
-        <f>C15*D15</f>
-        <v/>
-      </c>
-      <c r="F15" s="5">
-        <f>C4*C5</f>
-        <v/>
-      </c>
+        <f>E14/B4</f>
+        <v/>
+      </c>
+      <c r="F15" s="5" t="n"/>
       <c r="G15" s="5">
-        <f>C15*F15</f>
+        <f>G14/C4</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t>P04</t>
-        </is>
-      </c>
+      <c r="A16" s="4" t="n"/>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>研修カスタマイズ費</t>
-        </is>
-      </c>
-      <c r="C16" s="5" t="n">
-        <v>200000</v>
-      </c>
-      <c r="D16" s="5">
-        <f>IF(B9="あり",1,0)</f>
-        <v/>
-      </c>
-      <c r="E16" s="5">
-        <f>C16*D16</f>
-        <v/>
-      </c>
-      <c r="F16" s="5">
-        <f>IF(C9="あり",1,0)</f>
-        <v/>
-      </c>
+          <t>B案とA案の差額</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="n"/>
+      <c r="D16" s="5" t="n"/>
+      <c r="E16" s="5" t="n"/>
+      <c r="F16" s="5" t="n"/>
       <c r="G16" s="5">
-        <f>C16*F16</f>
+        <f>G14-E14</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="inlineStr">
-        <is>
-          <t>P05</t>
-        </is>
-      </c>
+      <c r="A17" s="4" t="n"/>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>事前アセスメント</t>
-        </is>
-      </c>
-      <c r="C17" s="5" t="n">
-        <v>3000</v>
-      </c>
-      <c r="D17" s="5">
-        <f>B4</f>
-        <v/>
-      </c>
-      <c r="E17" s="5">
-        <f>C17*D17</f>
-        <v/>
-      </c>
-      <c r="F17" s="5">
-        <f>C4</f>
-        <v/>
-      </c>
-      <c r="G17" s="5">
-        <f>C17*F17</f>
-        <v/>
+          <t>予算の目安（税抜・承認前）</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n"/>
+      <c r="D17" s="5" t="n"/>
+      <c r="E17" s="5" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="F17" s="5" t="n"/>
+      <c r="G17" s="5" t="n">
+        <v>1000000</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="4" t="inlineStr">
-        <is>
-          <t>P06</t>
-        </is>
-      </c>
+      <c r="A18" s="4" t="n"/>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>事後フォローアップ</t>
-        </is>
-      </c>
-      <c r="C18" s="5" t="n">
-        <v>100000</v>
-      </c>
-      <c r="D18" s="5">
-        <f>IF(B10="あり",1,0)</f>
-        <v/>
-      </c>
+          <t>目安との差（＋は目安内の余裕）</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n"/>
+      <c r="D18" s="5" t="n"/>
       <c r="E18" s="5">
-        <f>C18*D18</f>
-        <v/>
-      </c>
-      <c r="F18" s="5">
-        <f>IF(C10="あり",1,0)</f>
-        <v/>
-      </c>
+        <f>E17-E14</f>
+        <v/>
+      </c>
+      <c r="F18" s="5" t="n"/>
       <c r="G18" s="5">
-        <f>C18*F18</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="4" t="inlineStr">
-        <is>
-          <t>P07</t>
-        </is>
-      </c>
-      <c r="B19" s="4" t="inlineStr">
-        <is>
-          <t>ELI会場使用料</t>
-        </is>
-      </c>
-      <c r="C19" s="5" t="n">
-        <v>60000</v>
-      </c>
-      <c r="D19" s="5">
-        <f>IF(B7="ELI会場",B5,0)</f>
-        <v/>
-      </c>
-      <c r="E19" s="5">
-        <f>C19*D19</f>
-        <v/>
-      </c>
-      <c r="F19" s="5">
-        <f>IF(C7="ELI会場",C5,0)</f>
-        <v/>
-      </c>
-      <c r="G19" s="5">
-        <f>C19*F19</f>
+        <f>G17-G14</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="4" t="inlineStr">
-        <is>
-          <t>P08</t>
-        </is>
-      </c>
-      <c r="B20" s="4" t="inlineStr">
-        <is>
-          <t>オンライン配信運営費</t>
-        </is>
-      </c>
-      <c r="C20" s="5" t="n">
-        <v>50000</v>
-      </c>
-      <c r="D20" s="5">
-        <f>IF(B6="オンライン",B5,0)</f>
-        <v/>
-      </c>
-      <c r="E20" s="5">
-        <f>C20*D20</f>
-        <v/>
-      </c>
-      <c r="F20" s="5">
-        <f>IF(C6="オンライン",C5,0)</f>
-        <v/>
-      </c>
-      <c r="G20" s="5">
-        <f>C20*F20</f>
-        <v/>
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>想定：A案 600,000円（1名30,000円）／B案 1,000,000円（1名50,000円）／差額 400,000円（事前診断20万円＋活用フォロー20万円）</t>
+        </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="4" t="n"/>
-      <c r="B21" s="4" t="inlineStr">
-        <is>
-          <t>割引（2日以上で講師料5%）</t>
-        </is>
-      </c>
-      <c r="C21" s="5" t="n"/>
-      <c r="D21" s="5" t="n"/>
-      <c r="E21" s="5">
-        <f>IF(B5&gt;=2,-E13*0.05,0)</f>
-        <v/>
-      </c>
-      <c r="F21" s="5" t="n"/>
-      <c r="G21" s="5">
-        <f>IF(C5&gt;=2,-G13*0.05,0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="4" t="n"/>
-      <c r="B22" s="4" t="inlineStr">
-        <is>
-          <t>合計（税別）</t>
-        </is>
-      </c>
-      <c r="C22" s="5" t="n"/>
-      <c r="D22" s="5" t="n"/>
-      <c r="E22" s="5">
-        <f>SUM(E13:E21)</f>
-        <v/>
-      </c>
-      <c r="F22" s="5" t="n"/>
-      <c r="G22" s="5">
-        <f>SUM(G13:G21)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="4" t="n"/>
-      <c r="B23" s="4" t="inlineStr">
-        <is>
-          <t>予算の目安（税別・承認前）</t>
-        </is>
-      </c>
-      <c r="C23" s="5" t="n"/>
-      <c r="D23" s="5" t="n"/>
-      <c r="E23" s="5" t="n">
-        <v>1000000</v>
-      </c>
-      <c r="F23" s="5" t="n"/>
-      <c r="G23" s="5" t="n">
-        <v>1000000</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="4" t="n"/>
-      <c r="B24" s="4" t="inlineStr">
-        <is>
-          <t>予算との差額（＋は予算内）</t>
-        </is>
-      </c>
-      <c r="C24" s="5" t="n"/>
-      <c r="D24" s="5" t="n"/>
-      <c r="E24" s="5">
-        <f>E23-E22</f>
-        <v/>
-      </c>
-      <c r="F24" s="5" t="n"/>
-      <c r="G24" s="5">
-        <f>G23-G22</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>想定：A案 690,000円（予算内・31万円の余裕）／B案 1,195,000円（予算を19.5万円超過）</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>→ B案は「予算の承認額を引き上げる」か「アシスタント講師を外す（▲16万円）」などの調整案を用意して決裁者に説明する</t>
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>含まないもの：会場・端末・必要なライセンス（お客様で手配）、無制限の個別相談、アプリ開発</t>
         </is>
       </c>
     </row>
